--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486975_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486975_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.471</v>
+        <v>9.3612</v>
       </c>
       <c r="E2" t="n">
-        <v>10.2504</v>
+        <v>10.6959</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7794</v>
+        <v>-1.3348</v>
       </c>
       <c r="G2" t="n">
         <v>7.8797</v>
@@ -610,13 +610,13 @@
         <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6757</v>
+        <v>-0.7855</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4147</v>
+        <v>0.0308</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.2609</v>
+        <v>-0.8163</v>
       </c>
       <c r="V2" t="n">
         <v>0.8295</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0519</v>
+        <v>5.3571</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9727</v>
+        <v>5.5229</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0792</v>
+        <v>-0.1658</v>
       </c>
       <c r="G3" t="n">
         <v>3.7277</v>
@@ -688,13 +688,13 @@
         <v>2.0534</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5028</v>
+        <v>0.8079</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0268</v>
+        <v>0.577</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4759</v>
+        <v>0.2309</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3343</v>
+        <v>4.0236</v>
       </c>
       <c r="E4" t="n">
-        <v>7.243</v>
+        <v>6.5767</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.9087</v>
+        <v>-2.553</v>
       </c>
       <c r="G4" t="n">
         <v>5.3193</v>
@@ -766,13 +766,13 @@
         <v>1.6427</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4811</v>
+        <v>0.1705</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6114</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.1303</v>
+        <v>-0.7746</v>
       </c>
       <c r="V4" t="n">
         <v>-1.8768</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7126</v>
+        <v>3.6875</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3554</v>
+        <v>3.8857</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6428</v>
+        <v>-0.1982</v>
       </c>
       <c r="G5" t="n">
         <v>1.309</v>
@@ -844,13 +844,13 @@
         <v>1.8481</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.1754</v>
+        <v>-0.2005</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1044</v>
+        <v>0.4259</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.071</v>
+        <v>-0.6264</v>
       </c>
       <c r="V5" t="n">
         <v>4.0164</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6366</v>
+        <v>1.9849</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9175</v>
+        <v>1.088</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7191</v>
+        <v>0.8969</v>
       </c>
       <c r="G6" t="n">
         <v>1.7687</v>
@@ -922,13 +922,13 @@
         <v>0.616</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7687</v>
+        <v>-0.4203</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5192</v>
+        <v>-0.3488</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2494</v>
+        <v>-0.0716</v>
       </c>
       <c r="V6" t="n">
         <v>1.0472</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0909</v>
+        <v>-2.1509</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6143</v>
+        <v>-2.5557</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5233</v>
+        <v>0.4048</v>
       </c>
       <c r="G7" t="n">
         <v>-1.8487</v>
@@ -1000,13 +1000,13 @@
         <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>1.9898</v>
+        <v>0.9298</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6387</v>
+        <v>0.6973</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3512</v>
+        <v>0.2326</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.892</v>
+        <v>-2.3401</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2005</v>
+        <v>-1.6189</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6915</v>
+        <v>-0.7212</v>
       </c>
       <c r="G8" t="n">
         <v>-4.0109</v>
@@ -1078,13 +1078,13 @@
         <v>0.4107</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2277</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0072</v>
+        <v>0.5888</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2205</v>
+        <v>0.1909</v>
       </c>
       <c r="V8" t="n">
         <v>0.4805</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.105</v>
+        <v>-4.3076</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3967</v>
+        <v>-2.54</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7084</v>
+        <v>-1.7676</v>
       </c>
       <c r="G9" t="n">
         <v>-3.2937</v>
@@ -1156,13 +1156,13 @@
         <v>0.8214</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0922</v>
+        <v>-0.1104</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3098</v>
+        <v>0.1665</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2176</v>
+        <v>-0.2769</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6982</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.1802</v>
+        <v>-7.0188</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8505</v>
+        <v>-2.7188</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.3297</v>
+        <v>-4.3001</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4561</v>
@@ -1234,13 +1234,13 @@
         <v>0.4107</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3832</v>
+        <v>-0.2218</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2907</v>
+        <v>-0.159</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0925</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4661</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.938300000000001</v>
+        <v>8.596900000000002</v>
       </c>
       <c r="E11" t="n">
-        <v>17.677</v>
+        <v>18.3358</v>
       </c>
       <c r="F11" t="n">
-        <v>-9.738899999999999</v>
+        <v>-9.738999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>9.395000000000001</v>
@@ -1312,13 +1312,13 @@
         <v>10.2671</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2906000000000002</v>
+        <v>0.9493999999999998</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2649</v>
+        <v>2.9236</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.9741</v>
+        <v>-1.9742</v>
       </c>
       <c r="V11" t="n">
         <v>1.3325</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.0087</v>
+        <v>6.1613</v>
       </c>
       <c r="E12" t="n">
-        <v>4.2106</v>
+        <v>3.8968</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7981</v>
+        <v>2.2645</v>
       </c>
       <c r="G12" t="n">
         <v>2.3461</v>
@@ -1390,13 +1390,13 @@
         <v>1.8481</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6359</v>
+        <v>0.7885</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8096</v>
+        <v>0.4958</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8263</v>
+        <v>0.2928</v>
       </c>
       <c r="V12" t="n">
         <v>1.1786</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. ASO JIMENEZ</t>
+          <t>O. ALVARADO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5263</v>
+        <v>3.3436</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5107</v>
+        <v>7.6666</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0156</v>
+        <v>-4.323</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.056</v>
+        <v>4.8728</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0544</v>
+        <v>0.4764</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.1104</v>
+        <v>4.3964</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1195</v>
+        <v>8.6548</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6069</v>
+        <v>1.4989</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5127</v>
+        <v>7.156</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1756</v>
+        <v>-3.782</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4475</v>
+        <v>-1.0225</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.6231</v>
+        <v>-2.7596</v>
       </c>
       <c r="P13" t="n">
-        <v>1.0267</v>
+        <v>1.4374</v>
       </c>
       <c r="Q13" t="n">
+        <v>-1.2321</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.6694</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.1289</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.2438</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.3727</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-2.8377</v>
+      </c>
+      <c r="W13" t="n">
         <v>0</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.0267</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.9663</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.8018999999999999</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.1644</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.5893</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.5893</v>
-      </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-2.8377</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. ALVARADO RODRIGUEZ</t>
+          <t>P. ASO JIMENEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8704</v>
+        <v>1.8254</v>
       </c>
       <c r="E14" t="n">
-        <v>6.6205</v>
+        <v>1.9877</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.7501</v>
+        <v>-0.1623</v>
       </c>
       <c r="G14" t="n">
-        <v>4.8728</v>
+        <v>-0.056</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4764</v>
+        <v>1.0544</v>
       </c>
       <c r="I14" t="n">
-        <v>4.3964</v>
+        <v>-1.1104</v>
       </c>
       <c r="J14" t="n">
-        <v>8.6548</v>
+        <v>1.1195</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4989</v>
+        <v>0.6069</v>
       </c>
       <c r="L14" t="n">
-        <v>7.156</v>
+        <v>0.5127</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.782</v>
+        <v>-1.1756</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0225</v>
+        <v>0.4475</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.7596</v>
+        <v>-1.6231</v>
       </c>
       <c r="P14" t="n">
-        <v>1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.2321</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.6694</v>
+        <v>1.0267</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6021</v>
+        <v>0.2654</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8022</v>
+        <v>0.2788</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7998</v>
+        <v>-0.0134</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.8377</v>
+        <v>0.5893</v>
       </c>
       <c r="W14" t="n">
+        <v>0.5893</v>
+      </c>
+      <c r="X14" t="n">
         <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-2.8377</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. ARJOL LOPEZ</t>
+          <t>J. JIMÉNEZ JIMÉNEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.07489999999999999</v>
+        <v>0.2733</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6784</v>
+        <v>-0.199</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7534</v>
+        <v>0.4723</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9167999999999999</v>
+        <v>0.5658</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9697</v>
+        <v>0.3634</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0529</v>
+        <v>0.2023</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2558</v>
+        <v>1.5253</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1649</v>
+        <v>-0.6711</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4208</v>
+        <v>2.1963</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1726</v>
+        <v>-0.9595</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8047</v>
+        <v>1.0345</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3679</v>
+        <v>-1.994</v>
       </c>
       <c r="P15" t="n">
+        <v>-0.4107</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-2.0534</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.6427</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.0293</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.2402</v>
+      </c>
+      <c r="W15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-0.2053</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.2053</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-0.0965</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.0386</v>
-      </c>
-      <c r="U15" t="n">
-        <v>-0.1352</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.9384</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.5893</v>
-      </c>
       <c r="X15" t="n">
-        <v>0.3491</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ARAGONES NAVAIS</t>
+          <t>D. ARJOL LOPEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3664</v>
+        <v>0.1465</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3564</v>
+        <v>1.5738</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7228</v>
+        <v>-1.4273</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0253</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1487</v>
+        <v>-0.9697</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1234</v>
+        <v>0.0529</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5611</v>
+        <v>1.2558</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0614</v>
+        <v>-0.1649</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4997</v>
+        <v>1.4208</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5358</v>
+        <v>-2.1726</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0873</v>
+        <v>-0.8047</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6231</v>
+        <v>-1.3679</v>
       </c>
       <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-0.2053</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-2.0534</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.8481</v>
+        <v>0.2053</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0077</v>
+        <v>0.1249</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1513</v>
+        <v>-0.066</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1435</v>
+        <v>0.1909</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.1786</v>
+        <v>0.9384</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1786</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ JIMÉNEZ</t>
+          <t>A. ARAGONES NAVAIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7135</v>
+        <v>-0.2269</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.245</v>
+        <v>0.3564</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5315</v>
+        <v>-0.5834</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5658</v>
+        <v>1.0253</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3634</v>
+        <v>1.1487</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2023</v>
+        <v>-0.1234</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5253</v>
+        <v>2.5611</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6711</v>
+        <v>1.0614</v>
       </c>
       <c r="L17" t="n">
-        <v>2.1963</v>
+        <v>1.4997</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9595</v>
+        <v>-1.5358</v>
       </c>
       <c r="N17" t="n">
-        <v>1.0345</v>
+        <v>0.0873</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.994</v>
+        <v>-1.6231</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4107</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6427</v>
+        <v>1.8481</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6283</v>
+        <v>0.1317</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7169</v>
+        <v>-0.1513</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0886</v>
+        <v>0.283</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.4262</v>
+        <v>-3.2815</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.6454</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.8854</v>
+        <v>-2.6361</v>
       </c>
       <c r="G18" t="n">
         <v>-3.2987</v>
@@ -1858,13 +1858,13 @@
         <v>0.616</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.415</v>
+        <v>-0.2703</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1122</v>
+        <v>0.0076</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5272</v>
+        <v>-0.2779</v>
       </c>
       <c r="V18" t="n">
         <v>0.6982</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.2397</v>
+        <v>-3.5737</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9935</v>
+        <v>-0.7843</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.2463</v>
+        <v>-2.7895</v>
       </c>
       <c r="G19" t="n">
         <v>-3.0107</v>
@@ -1936,13 +1936,13 @@
         <v>0.8214</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.73</v>
+        <v>-0.064</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1513</v>
+        <v>0.0579</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5788</v>
+        <v>-0.122</v>
       </c>
       <c r="V19" t="n">
         <v>0.9384</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.4497</v>
+        <v>-4.4165</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5794</v>
+        <v>-2.8932</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8703</v>
+        <v>-1.5233</v>
       </c>
       <c r="G20" t="n">
         <v>-5.9408</v>
@@ -2014,13 +2014,13 @@
         <v>2.0534</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0284</v>
+        <v>0.0048</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9218</v>
+        <v>0.608</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9502</v>
+        <v>-0.6032</v>
       </c>
       <c r="V20" t="n">
         <v>0.6982</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.073</v>
+        <v>-6.7948</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.279</v>
+        <v>-1.2204</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.794</v>
+        <v>-5.5744</v>
       </c>
       <c r="G21" t="n">
         <v>-4.9818</v>
@@ -2092,13 +2092,13 @@
         <v>0.616</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6151</v>
+        <v>-0.1066</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1117</v>
+        <v>0.1703</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4966</v>
+        <v>-0.2769</v>
       </c>
       <c r="V21" t="n">
         <v>-2.117</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.938000000000001</v>
+        <v>-6.5433</v>
       </c>
       <c r="E22" t="n">
-        <v>9.738899999999999</v>
+        <v>9.739000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-17.6771</v>
+        <v>-16.2825</v>
       </c>
       <c r="G22" t="n">
         <v>-9.3948</v>
@@ -2140,13 +2140,13 @@
         <v>-1.9616</v>
       </c>
       <c r="I22" t="n">
-        <v>-7.433299999999999</v>
+        <v>-7.433300000000001</v>
       </c>
       <c r="J22" t="n">
         <v>14.4734</v>
       </c>
       <c r="K22" t="n">
-        <v>3.702699999999999</v>
+        <v>3.7027</v>
       </c>
       <c r="L22" t="n">
         <v>10.7709</v>
@@ -2170,19 +2170,19 @@
         <v>13.3471</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2907000000000004</v>
+        <v>1.1039</v>
       </c>
       <c r="T22" t="n">
         <v>1.9741</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.265</v>
+        <v>-0.8700999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-1.3324</v>
       </c>
       <c r="W22" t="n">
-        <v>3.558400000000001</v>
+        <v>3.5584</v>
       </c>
       <c r="X22" t="n">
         <v>-4.8908</v>
